--- a/satisfaction_surveys/041_pet_training_program_satisfaction_survey--satisfaction_surveys.xlsx
+++ b/satisfaction_surveys/041_pet_training_program_satisfaction_survey--satisfaction_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1010,8 +1010,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1056,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1090,12 +1090,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1107,12 +1107,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1141,12 +1141,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1158,12 +1158,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1175,12 +1175,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'extremely_satisfied'}</t>
+          <t>extremely_satisfied</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Extremely Satisfied'}</t>
+          <t>Extremely Satisfied</t>
         </is>
       </c>
     </row>
@@ -1192,12 +1192,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'satisfied'}</t>
+          <t>satisfied</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Satisfied'}</t>
+          <t>Satisfied</t>
         </is>
       </c>
     </row>
@@ -1209,12 +1209,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'dissatisfied'}</t>
+          <t>dissatisfied</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Dissatisfied'}</t>
+          <t>Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1243,12 +1243,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'extremely_dissatisfied'}</t>
+          <t>extremely_dissatisfied</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Extremely Dissatisfied'}</t>
+          <t>Extremely Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1294,12 +1294,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1311,12 +1311,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1328,12 +1328,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1345,12 +1345,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1362,12 +1362,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1379,12 +1379,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1396,12 +1396,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'on_time'}</t>
+          <t>on_time</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'On Time'}</t>
+          <t>On Time</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'sometimes'}</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Sometimes'}</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
@@ -1430,12 +1430,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'late'}</t>
+          <t>late</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Late'}</t>
+          <t>Late</t>
         </is>
       </c>
     </row>
@@ -1447,12 +1447,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'reasonable'}</t>
+          <t>reasonable</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Reasonable'}</t>
+          <t>Reasonable</t>
         </is>
       </c>
     </row>
@@ -1464,12 +1464,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'expensive'}</t>
+          <t>expensive</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Expensive'}</t>
+          <t>Expensive</t>
         </is>
       </c>
     </row>
@@ -1481,12 +1481,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'very_expensive'}</t>
+          <t>very_expensive</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Very Expensive'}</t>
+          <t>Very Expensive</t>
         </is>
       </c>
     </row>
@@ -1498,12 +1498,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'recommend_to_friends'}</t>
+          <t>recommend_to_friends</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Recommend to friends'}</t>
+          <t>Recommend to friends</t>
         </is>
       </c>
     </row>
@@ -1515,12 +1515,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'do_not_recommend'}</t>
+          <t>do_not_recommend</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Do not recommend'}</t>
+          <t>Do not recommend</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'undecided'}</t>
+          <t>undecided</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Undecided'}</t>
+          <t>Undecided</t>
         </is>
       </c>
     </row>
@@ -1549,12 +1549,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1566,12 +1566,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1583,12 +1583,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'undecided'}</t>
+          <t>undecided</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'Undecided'}</t>
+          <t>Undecided</t>
         </is>
       </c>
     </row>
